--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1C座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -31744,6125 +31603,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第1A期 - 1A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>258 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>110 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>129 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1908呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 431呎 (2房)
-$1,376万
-$31,933/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,452万
-$32,044/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$990万
-$31,022/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 431呎 (2房)
-$1,356万
-$31,457/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,430万
-$31,572/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$980万
-$30,715/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 431呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$3,054万
-$37,291/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$970万
-$30,408/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,193万
-$27,606/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$3,024万
-$36,921/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$3,730万
-$45,605/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$845万
-$26,495/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 431呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,388万
-$30,642/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$837万
-$26,232/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,169万
-$27,062/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,280万
-$28,267/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$4,034万
-$49,252/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$3,867万
-$47,278/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$828万
-$25,891/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,158万
-$26,796/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,361万
-$30,038/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$3,287万
-$40,136/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$797万
-$24,903/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,124万
-$26,019/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-$1,347万
-$29,742/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$3,066万
-$37,441/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,950万
-$36,070/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$793万
-$24,778/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,096万
-$25,382/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,226万
-$27,122/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,993万
-$36,545/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,991万
-$36,566/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$789万
-$24,656/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,091万
-$25,255/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,248万
-$27,602/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,949万
-$36,009/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$770万
-$24,050/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,086万
-$25,130/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,934万
-$35,829/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,907万
-$35,533/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$781万
-$24,412/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,102万
-$25,507/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,920万
-$35,653/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,838万
-$34,689/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$777万
-$24,291/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,096万
-$25,377/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,906万
-$35,480/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,796万
-$34,185/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$758万
-$23,694/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,069万
-$24,755/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,835万
-$34,613/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,702万
-$33,029/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$770万
-$24,047/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,064万
-$24,632/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,167万
-$25,825/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,823万
-$34,466/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,822万
-$34,501/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$768万
-$24,066/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,080万
-$25,000/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,162万
-$25,697/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 431呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,834万
-$34,601/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,701万
-$33,015/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$754万
-$23,569/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,064万
-$24,627/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,122万
-$24,827/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,792万
-$34,088/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,713万
-$33,171/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$750万
-$23,453/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,038万
-$24,021/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,116万
-$24,701/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,751万
-$33,587/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,622万
-$32,051/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$732万
-$22,875/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,032万
-$23,900/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,111万
-$24,577/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,736万
-$33,410/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,608万
-$31,884/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$728万
-$22,762/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,027万
-$23,782/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,105万
-$24,456/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,806万
-$34,261/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,595万
-$31,724/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$725万
-$22,647/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,022万
-$23,664/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,100万
-$24,332/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,792万
-$34,090/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,582万
-$31,565/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$721万
-$22,534/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,017万
-$23,544/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,094万
-$24,210/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,722万
-$33,242/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,569万
-$31,407/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$718万
-$22,422/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,022万
-$23,662/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,089万
-$24,091/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J29" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,682万
-$32,744/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,531万
-$30,936/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$707万
-$22,084/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$1,007万
-$23,308/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,073万
-$23,730/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J30" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,629万
-$32,098/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,505万
-$30,627/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$716万
-$22,433/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$987万
-$22,845/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,062万
-$23,493/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,603万
-$31,780/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,480万
-$30,320/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>C | 319呎 (1房)
-$708万
-$22,207/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>D | 431呎 (2房)
-$999万
-$23,183/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,051万
-$23,257/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,563万
-$31,297/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,443万
-$29,866/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$682万
-$21,322/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$962万
-$22,278/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,036万
-$22,909/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>A | 819呎 (3房)
-$2,525万
-$30,827/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>B | 818呎 (3房)
-$2,406万
-$29,418/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>C | 320呎 (1房)
-$672万
-$21,000/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>D | 432呎 (2房)
-$948万
-$21,942/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>E | 452呎 (2房)
-$1,020万
-$22,564/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 426呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
-        <is>
-          <t>G | 297呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>H | 298呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>J | 290呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第1A期 - 1B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>174 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>22 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>135 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,488万
-$33,145/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,466万
-$32,657/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,409万
-$31,383/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,395万
-$31,073/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,381万
-$30,766/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,251万
-$27,853/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,198万
-$26,670/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-$1,565万
-$28,560/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,180万
-$26,274/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,151万
-$25,628/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,145万
-$25,501/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-$1,519万
-$27,714/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,150万
-$25,624/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-$1,511万
-$27,577/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,145万
-$25,494/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,139万
-$25,367/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,111万
-$24,744/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,106万
-$24,621/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,100万
-$24,499/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-$1,474万
-$26,894/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,116万
-$24,864/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="19" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(在售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-$1,452万
-$26,489/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,078万
-$24,009/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,089万
-$24,247/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,057万
-$23,532/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,041万
-$23,178/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>A | 548呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>B | 449呎 (2房)
-$1,025万
-$22,831/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 444呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 315呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 493呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港．湾畔第1A期 - 1C座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>203 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>21 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>174 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,839万
-$35,856/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,812万
-$35,324/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,794万
-$34,973/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,741万
-$33,945/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-$828万
-$26,812/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,724万
-$33,608/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,553万
-$30,281/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,487万
-$28,992/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,538万
-$29,979/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,501万
-$29,267/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,494万
-$29,121/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,458万
-$28,419/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,451万
-$28,279/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,443万
-$28,135/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,422万
-$27,715/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,387万
-$27,035/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,380万
-$26,901/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,373万
-$26,766/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G27" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,366万
-$26,632/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,359万
-$26,499/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,353万
-$26,366/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F30" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G30" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,347万
-$26,265/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F31" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,334万
-$26,004/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F32" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,306万
-$25,454/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G33" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,286万
-$25,072/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>A | 451呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="16" t="inlineStr">
-        <is>
-          <t>B | 489呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="inlineStr">
-        <is>
-          <t>C | 309呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="inlineStr">
-        <is>
-          <t>E | 305呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G34" s="16" t="inlineStr">
-        <is>
-          <t>F | 442呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>G | 513呎 (2房)
-$1,267万
-$24,696/呎
-(26年-01月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1B座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1C座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +149,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +230,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +663,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -31603,4 +31792,6125 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1908呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 431呎 (2房)
+$1376万
+$31,933/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1452万
+$32,044/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$990万
+$31,022/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 431呎 (2房)
+$1356万
+$31,457/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1430万
+$31,572/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$980万
+$30,715/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 431呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$3054万
+$37,291/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$970万
+$30,408/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1193万
+$27,606/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$3024万
+$36,921/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$3730万
+$45,605/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$845万
+$26,495/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 431呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1388万
+$30,642/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$837万
+$26,232/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1169万
+$27,062/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1280万
+$28,267/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$4034万
+$49,252/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$3867万
+$47,278/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$828万
+$25,891/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1158万
+$26,796/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1361万
+$30,038/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$3287万
+$40,136/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$797万
+$24,903/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1124万
+$26,019/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+$1347万
+$29,742/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$3066万
+$37,441/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2950万
+$36,070/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$793万
+$24,778/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1096万
+$25,382/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1226万
+$27,122/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2993万
+$36,545/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2991万
+$36,566/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$789万
+$24,656/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1091万
+$25,255/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1248万
+$27,602/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2949万
+$36,009/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$770万
+$24,050/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1086万
+$25,130/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2934万
+$35,829/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2907万
+$35,533/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$781万
+$24,412/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1102万
+$25,507/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2920万
+$35,653/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2838万
+$34,689/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$777万
+$24,291/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1096万
+$25,377/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2906万
+$35,480/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2796万
+$34,185/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$758万
+$23,694/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1069万
+$24,755/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2835万
+$34,613/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2702万
+$33,029/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$770万
+$24,047/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1064万
+$24,632/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1167万
+$25,825/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2823万
+$34,466/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2822万
+$34,501/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$768万
+$24,066/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1080万
+$25,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1162万
+$25,697/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 431呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2834万
+$34,601/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2701万
+$33,015/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$754万
+$23,569/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1064万
+$24,627/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1122万
+$24,827/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2792万
+$34,088/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2713万
+$33,171/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$750万
+$23,453/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1038万
+$24,021/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1116万
+$24,701/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2751万
+$33,587/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2622万
+$32,051/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$732万
+$22,875/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1032万
+$23,900/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1111万
+$24,577/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2736万
+$33,410/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2608万
+$31,884/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$728万
+$22,762/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1027万
+$23,782/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1105万
+$24,456/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2806万
+$34,261/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2595万
+$31,724/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$725万
+$22,647/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1022万
+$23,664/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1100万
+$24,332/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2792万
+$34,090/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2582万
+$31,565/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$721万
+$22,534/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1017万
+$23,544/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1094万
+$24,210/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2722万
+$33,242/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2569万
+$31,407/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$718万
+$22,422/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1022万
+$23,662/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1089万
+$24,091/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2682万
+$32,744/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2531万
+$30,936/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$707万
+$22,084/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$1007万
+$23,308/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1073万
+$23,730/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2629万
+$32,098/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2505万
+$30,627/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$716万
+$22,433/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$987万
+$22,845/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1062万
+$23,493/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J30" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2603万
+$31,780/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2480万
+$30,320/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>C | 319呎 (1房)
+$708万
+$22,207/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>D | 431呎 (2房)
+$999万
+$23,183/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1051万
+$23,257/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J31" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2563万
+$31,297/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2443万
+$29,866/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$682万
+$21,322/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$962万
+$22,278/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1036万
+$22,909/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I32" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J32" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>A | 819呎 (3房)
+$2525万
+$30,827/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>B | 818呎 (3房)
+$2406万
+$29,418/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>C | 320呎 (1房)
+$672万
+$21,000/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>D | 432呎 (2房)
+$948万
+$21,942/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>E | 452呎 (2房)
+$1020万
+$22,564/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 426呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H33" s="20" t="inlineStr">
+        <is>
+          <t>G | 297呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>H | 298呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J33" s="20" t="inlineStr">
+        <is>
+          <t>J | 290呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1488万
+$33,145/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1466万
+$32,657/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1409万
+$31,383/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1395万
+$31,073/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1381万
+$30,766/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1251万
+$27,853/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1198万
+$26,670/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+$1565万
+$28,560/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1180万
+$26,274/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1151万
+$25,628/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1145万
+$25,501/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+$1519万
+$27,714/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1150万
+$25,624/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+$1511万
+$27,577/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1145万
+$25,494/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1139万
+$25,367/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1111万
+$24,744/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1106万
+$24,621/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1100万
+$24,499/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+$1474万
+$26,894/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1116万
+$24,864/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+$1452万
+$26,489/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1078万
+$24,009/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1089万
+$24,247/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1057万
+$23,532/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1041万
+$23,178/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>A | 548呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>B | 449呎 (2房)
+$1025万
+$22,831/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 444呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 315呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 493呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1C座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1839万
+$35,856/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1812万
+$35,324/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1794万
+$34,973/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1741万
+$33,945/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+$828万
+$26,812/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1724万
+$33,608/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1553万
+$30,281/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1487万
+$28,992/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1538万
+$29,979/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1501万
+$29,267/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1494万
+$29,121/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1458万
+$28,419/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1451万
+$28,279/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1443万
+$28,135/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1422万
+$27,715/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1387万
+$27,035/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1380万
+$26,901/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1373万
+$26,766/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1366万
+$26,632/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1359万
+$26,499/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1353万
+$26,366/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G29" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1347万
+$26,265/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G30" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1334万
+$26,004/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G31" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1306万
+$25,454/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F32" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1286万
+$25,072/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>A | 451呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>B | 489呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>C | 309呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>E | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G33" s="20" t="inlineStr">
+        <is>
+          <t>F | 442呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>G | 513呎 (2房)
+$1267万
+$24,696/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -663,7 +663,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -4022,14 +4022,14 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
         <v>8368000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>26232</v>
+        <v>26150</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>8368000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>26232</v>
+        <v>26150</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -44360,10 +44360,10 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>C | 319呎 (1房)
+          <t>C | 320呎 (1房)
 $837万
-$26,232/呎
-(26年-06月-21日)</t>
+$26,150/呎
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -47038,7 +47038,7 @@
           <t>A | 548呎 (2房)
 $1565万
 $28,560/呎
-(26年-06月-24日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -47643,7 +47643,7 @@
           <t>A | 548呎 (2房)
 $1474万
 $26,894/呎
-(26年-06月-21日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">

--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -44189,7 +44189,7 @@
           <t>A | 819呎 (3房)
 $3054万
 $37,291/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -44213,7 +44213,7 @@
           <t>D | 432呎 (2房)
 $1193万
 $27,606/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -44268,7 +44268,7 @@
           <t>A | 819呎 (3房)
 $3024万
 $36,921/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -44276,7 +44276,7 @@
           <t>B | 818呎 (3房)
 $3730万
 $45,605/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -44284,7 +44284,7 @@
           <t>C | 319呎 (1房)
 $845万
 $26,495/呎
-(26年-06月-30日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -44363,7 +44363,7 @@
           <t>C | 320呎 (1房)
 $837万
 $26,150/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -44371,7 +44371,7 @@
           <t>D | 432呎 (2房)
 $1169万
 $27,062/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -44379,7 +44379,7 @@
           <t>E | 453呎 (2房)
 $1280万
 $28,267/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -44426,7 +44426,7 @@
           <t>A | 819呎 (3房)
 $4034万
 $49,252/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -44434,7 +44434,7 @@
           <t>B | 818呎 (3房)
 $3867万
 $47,278/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -44442,7 +44442,7 @@
           <t>C | 320呎 (1房)
 $828万
 $25,891/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -44450,7 +44450,7 @@
           <t>D | 432呎 (2房)
 $1158万
 $26,796/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -44505,7 +44505,7 @@
           <t>A | 819呎 (3房)
 $3287万
 $40,136/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44521,7 +44521,7 @@
           <t>C | 320呎 (1房)
 $797万
 $24,903/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -44529,7 +44529,7 @@
           <t>D | 432呎 (2房)
 $1124万
 $26,019/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -44584,7 +44584,7 @@
           <t>A | 819呎 (3房)
 $3066万
 $37,441/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -44592,7 +44592,7 @@
           <t>B | 818呎 (3房)
 $2950万
 $36,070/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
@@ -44600,7 +44600,7 @@
           <t>C | 320呎 (1房)
 $793万
 $24,778/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -44608,7 +44608,7 @@
           <t>D | 432呎 (2房)
 $1096万
 $25,382/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -44616,7 +44616,7 @@
           <t>E | 452呎 (2房)
 $1226万
 $27,122/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -44663,7 +44663,7 @@
           <t>A | 819呎 (3房)
 $2993万
 $36,545/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -44671,7 +44671,7 @@
           <t>B | 818呎 (3房)
 $2991万
 $36,566/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
@@ -44679,7 +44679,7 @@
           <t>C | 320呎 (1房)
 $789万
 $24,656/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -44687,7 +44687,7 @@
           <t>D | 432呎 (2房)
 $1091万
 $25,255/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -44695,7 +44695,7 @@
           <t>E | 452呎 (2房)
 $1248万
 $27,602/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -44742,7 +44742,7 @@
           <t>A | 819呎 (3房)
 $2949万
 $36,009/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -44758,7 +44758,7 @@
           <t>C | 320呎 (1房)
 $770万
 $24,050/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -44766,7 +44766,7 @@
           <t>D | 432呎 (2房)
 $1086万
 $25,130/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -44821,7 +44821,7 @@
           <t>A | 819呎 (3房)
 $2934万
 $35,829/呎
-(25年-10月-26日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -44829,7 +44829,7 @@
           <t>B | 818呎 (3房)
 $2907万
 $35,533/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -44837,7 +44837,7 @@
           <t>C | 320呎 (1房)
 $781万
 $24,412/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -44845,7 +44845,7 @@
           <t>D | 432呎 (2房)
 $1102万
 $25,507/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -44900,7 +44900,7 @@
           <t>A | 819呎 (3房)
 $2920万
 $35,653/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -44908,7 +44908,7 @@
           <t>B | 818呎 (3房)
 $2838万
 $34,689/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -44916,7 +44916,7 @@
           <t>C | 320呎 (1房)
 $777万
 $24,291/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -44924,7 +44924,7 @@
           <t>D | 432呎 (2房)
 $1096万
 $25,377/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -44979,7 +44979,7 @@
           <t>A | 819呎 (3房)
 $2906万
 $35,480/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -44987,7 +44987,7 @@
           <t>B | 818呎 (3房)
 $2796万
 $34,185/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -44995,7 +44995,7 @@
           <t>C | 320呎 (1房)
 $758万
 $23,694/呎
-(26年-03月-11日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -45003,7 +45003,7 @@
           <t>D | 432呎 (2房)
 $1069万
 $24,755/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -45058,7 +45058,7 @@
           <t>A | 819呎 (3房)
 $2835万
 $34,613/呎
-(25年-09月-02日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -45066,7 +45066,7 @@
           <t>B | 818呎 (3房)
 $2702万
 $33,029/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -45074,7 +45074,7 @@
           <t>C | 320呎 (1房)
 $770万
 $24,047/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -45082,7 +45082,7 @@
           <t>D | 432呎 (2房)
 $1064万
 $24,632/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -45090,7 +45090,7 @@
           <t>E | 452呎 (2房)
 $1167万
 $25,825/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -45137,7 +45137,7 @@
           <t>A | 819呎 (3房)
 $2823万
 $34,466/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -45145,7 +45145,7 @@
           <t>B | 818呎 (3房)
 $2822万
 $34,501/呎
-(26年-03月-09日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -45153,7 +45153,7 @@
           <t>C | 319呎 (1房)
 $768万
 $24,066/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -45161,7 +45161,7 @@
           <t>D | 432呎 (2房)
 $1080万
 $25,000/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -45169,7 +45169,7 @@
           <t>E | 452呎 (2房)
 $1162万
 $25,697/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -45295,7 +45295,7 @@
           <t>A | 819呎 (3房)
 $2834万
 $34,601/呎
-(25年-09月-16日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -45303,7 +45303,7 @@
           <t>B | 818呎 (3房)
 $2701万
 $33,015/呎
-(26年-01月-01日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -45311,7 +45311,7 @@
           <t>C | 320呎 (1房)
 $754万
 $23,569/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -45319,7 +45319,7 @@
           <t>D | 432呎 (2房)
 $1064万
 $24,627/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -45327,7 +45327,7 @@
           <t>E | 452呎 (2房)
 $1122万
 $24,827/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -45374,7 +45374,7 @@
           <t>A | 819呎 (3房)
 $2792万
 $34,088/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -45382,7 +45382,7 @@
           <t>B | 818呎 (3房)
 $2713万
 $33,171/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
@@ -45390,7 +45390,7 @@
           <t>C | 320呎 (1房)
 $750万
 $23,453/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -45398,7 +45398,7 @@
           <t>D | 432呎 (2房)
 $1038万
 $24,021/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -45406,7 +45406,7 @@
           <t>E | 452呎 (2房)
 $1116万
 $24,701/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -45453,7 +45453,7 @@
           <t>A | 819呎 (3房)
 $2751万
 $33,587/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -45461,7 +45461,7 @@
           <t>B | 818呎 (3房)
 $2622万
 $32,051/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -45469,7 +45469,7 @@
           <t>C | 320呎 (1房)
 $732万
 $22,875/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -45477,7 +45477,7 @@
           <t>D | 432呎 (2房)
 $1032万
 $23,900/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -45485,7 +45485,7 @@
           <t>E | 452呎 (2房)
 $1111万
 $24,577/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -45532,7 +45532,7 @@
           <t>A | 819呎 (3房)
 $2736万
 $33,410/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -45540,7 +45540,7 @@
           <t>B | 818呎 (3房)
 $2608万
 $31,884/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -45548,7 +45548,7 @@
           <t>C | 320呎 (1房)
 $728万
 $22,762/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -45556,7 +45556,7 @@
           <t>D | 432呎 (2房)
 $1027万
 $23,782/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -45564,7 +45564,7 @@
           <t>E | 452呎 (2房)
 $1105万
 $24,456/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -45611,7 +45611,7 @@
           <t>A | 819呎 (3房)
 $2806万
 $34,261/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -45619,7 +45619,7 @@
           <t>B | 818呎 (3房)
 $2595万
 $31,724/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
@@ -45627,7 +45627,7 @@
           <t>C | 320呎 (1房)
 $725万
 $22,647/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -45635,7 +45635,7 @@
           <t>D | 432呎 (2房)
 $1022万
 $23,664/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -45643,7 +45643,7 @@
           <t>E | 452呎 (2房)
 $1100万
 $24,332/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -45690,7 +45690,7 @@
           <t>A | 819呎 (3房)
 $2792万
 $34,090/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -45698,7 +45698,7 @@
           <t>B | 818呎 (3房)
 $2582万
 $31,565/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -45706,7 +45706,7 @@
           <t>C | 320呎 (1房)
 $721万
 $22,534/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -45714,7 +45714,7 @@
           <t>D | 432呎 (2房)
 $1017万
 $23,544/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -45722,7 +45722,7 @@
           <t>E | 452呎 (2房)
 $1094万
 $24,210/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -45769,7 +45769,7 @@
           <t>A | 819呎 (3房)
 $2722万
 $33,242/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -45777,7 +45777,7 @@
           <t>B | 818呎 (3房)
 $2569万
 $31,407/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
@@ -45785,7 +45785,7 @@
           <t>C | 320呎 (1房)
 $718万
 $22,422/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -45793,7 +45793,7 @@
           <t>D | 432呎 (2房)
 $1022万
 $23,662/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
@@ -45801,7 +45801,7 @@
           <t>E | 452呎 (2房)
 $1089万
 $24,091/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -45848,7 +45848,7 @@
           <t>A | 819呎 (3房)
 $2682万
 $32,744/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -45856,7 +45856,7 @@
           <t>B | 818呎 (3房)
 $2531万
 $30,936/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -45864,7 +45864,7 @@
           <t>C | 320呎 (1房)
 $707万
 $22,084/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -45872,7 +45872,7 @@
           <t>D | 432呎 (2房)
 $1007万
 $23,308/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -45880,7 +45880,7 @@
           <t>E | 452呎 (2房)
 $1073万
 $23,730/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -45927,7 +45927,7 @@
           <t>A | 819呎 (3房)
 $2629万
 $32,098/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -45935,7 +45935,7 @@
           <t>B | 818呎 (3房)
 $2505万
 $30,627/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
@@ -45943,7 +45943,7 @@
           <t>C | 319呎 (1房)
 $716万
 $22,433/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -45951,7 +45951,7 @@
           <t>D | 432呎 (2房)
 $987万
 $22,845/呎
-(25年-12月-22日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
@@ -45959,7 +45959,7 @@
           <t>E | 452呎 (2房)
 $1062万
 $23,493/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -46006,7 +46006,7 @@
           <t>A | 819呎 (3房)
 $2603万
 $31,780/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -46014,7 +46014,7 @@
           <t>B | 818呎 (3房)
 $2480万
 $30,320/呎
-(25年-09月-08日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
@@ -46022,7 +46022,7 @@
           <t>C | 319呎 (1房)
 $708万
 $22,207/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -46030,7 +46030,7 @@
           <t>D | 431呎 (2房)
 $999万
 $23,183/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -46038,7 +46038,7 @@
           <t>E | 452呎 (2房)
 $1051万
 $23,257/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -46085,7 +46085,7 @@
           <t>A | 819呎 (3房)
 $2563万
 $31,297/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -46093,7 +46093,7 @@
           <t>B | 818呎 (3房)
 $2443万
 $29,866/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
@@ -46101,7 +46101,7 @@
           <t>C | 320呎 (1房)
 $682万
 $21,322/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -46109,7 +46109,7 @@
           <t>D | 432呎 (2房)
 $962万
 $22,278/呎
-(26年-01月-07日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
@@ -46117,7 +46117,7 @@
           <t>E | 452呎 (2房)
 $1036万
 $22,909/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -46164,7 +46164,7 @@
           <t>A | 819呎 (3房)
 $2525万
 $30,827/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -46172,7 +46172,7 @@
           <t>B | 818呎 (3房)
 $2406万
 $29,418/呎
-(25年-09月-11日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
@@ -46180,7 +46180,7 @@
           <t>C | 320呎 (1房)
 $672万
 $21,000/呎
-(26年-01月-13日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -46188,7 +46188,7 @@
           <t>D | 432呎 (2房)
 $948万
 $21,942/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -46196,7 +46196,7 @@
           <t>E | 452呎 (2房)
 $1020万
 $22,564/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -46881,7 +46881,7 @@
           <t>B | 449呎 (2房)
 $1251万
 $27,853/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -46936,7 +46936,7 @@
           <t>B | 449呎 (2房)
 $1198万
 $26,670/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -47038,7 +47038,7 @@
           <t>A | 548呎 (2房)
 $1565万
 $28,560/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -47101,7 +47101,7 @@
           <t>B | 449呎 (2房)
 $1180万
 $26,274/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -47156,7 +47156,7 @@
           <t>B | 449呎 (2房)
 $1151万
 $25,628/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -47211,7 +47211,7 @@
           <t>B | 449呎 (2房)
 $1145万
 $25,501/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -47313,7 +47313,7 @@
           <t>A | 548呎 (2房)
 $1519万
 $27,714/呎
-(26年-07月-12日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -47321,7 +47321,7 @@
           <t>B | 449呎 (2房)
 $1150万
 $25,624/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -47368,7 +47368,7 @@
           <t>A | 548呎 (2房)
 $1511万
 $27,577/呎
-(26年-06月-20日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -47376,7 +47376,7 @@
           <t>B | 449呎 (2房)
 $1145万
 $25,494/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47431,7 +47431,7 @@
           <t>B | 449呎 (2房)
 $1139万
 $25,367/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -47486,7 +47486,7 @@
           <t>B | 449呎 (2房)
 $1111万
 $24,744/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -47541,7 +47541,7 @@
           <t>B | 449呎 (2房)
 $1106万
 $24,621/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -47596,7 +47596,7 @@
           <t>B | 449呎 (2房)
 $1100万
 $24,499/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -47643,7 +47643,7 @@
           <t>A | 548呎 (2房)
 $1474万
 $26,894/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -47651,7 +47651,7 @@
           <t>B | 449呎 (2房)
 $1116万
 $24,864/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -47698,7 +47698,7 @@
           <t>A | 548呎 (2房)
 $1452万
 $26,489/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -47706,7 +47706,7 @@
           <t>B | 449呎 (2房)
 $1078万
 $24,009/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -47761,7 +47761,7 @@
           <t>B | 449呎 (2房)
 $1089万
 $24,247/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -47816,7 +47816,7 @@
           <t>B | 449呎 (2房)
 $1057万
 $23,532/呎
-(25年-12月-02日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -47871,7 +47871,7 @@
           <t>B | 449呎 (2房)
 $1041万
 $23,178/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -47926,7 +47926,7 @@
           <t>B | 449呎 (2房)
 $1025万
 $22,831/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -48508,7 +48508,7 @@
           <t>C | 309呎 (1房)
 $828万
 $26,812/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -48603,7 +48603,7 @@
           <t>G | 513呎 (2房)
 $1591万
 $31,006/呎
-(26年-07月-09日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -48666,7 +48666,7 @@
           <t>G | 513呎 (2房)
 $1553万
 $30,281/呎
-(26年-06月-24日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -48729,7 +48729,7 @@
           <t>G | 513呎 (2房)
 $1487万
 $28,992/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -48792,7 +48792,7 @@
           <t>G | 513呎 (2房)
 $1538万
 $29,979/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -48855,7 +48855,7 @@
           <t>G | 513呎 (2房)
 $1501万
 $29,267/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -48918,7 +48918,7 @@
           <t>G | 513呎 (2房)
 $1494万
 $29,121/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -48981,7 +48981,7 @@
           <t>G | 513呎 (2房)
 $1458万
 $28,419/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -49044,7 +49044,7 @@
           <t>G | 513呎 (2房)
 $1451万
 $28,279/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -49107,7 +49107,7 @@
           <t>G | 513呎 (2房)
 $1443万
 $28,135/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -49233,7 +49233,7 @@
           <t>G | 513呎 (2房)
 $1422万
 $27,715/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -49296,7 +49296,7 @@
           <t>G | 513呎 (2房)
 $1387万
 $27,035/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -49359,7 +49359,7 @@
           <t>G | 513呎 (2房)
 $1380万
 $26,901/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -49422,7 +49422,7 @@
           <t>G | 513呎 (2房)
 $1373万
 $26,766/呎
-(26年-01月-19日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -49485,7 +49485,7 @@
           <t>G | 513呎 (2房)
 $1366万
 $26,632/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -49548,7 +49548,7 @@
           <t>G | 513呎 (2房)
 $1359万
 $26,499/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -49611,7 +49611,7 @@
           <t>G | 513呎 (2房)
 $1353万
 $26,366/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -49674,7 +49674,7 @@
           <t>G | 513呎 (2房)
 $1347万
 $26,265/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -49737,7 +49737,7 @@
           <t>G | 513呎 (2房)
 $1334万
 $26,004/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -49800,7 +49800,7 @@
           <t>G | 513呎 (2房)
 $1306万
 $25,454/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -49863,7 +49863,7 @@
           <t>G | 513呎 (2房)
 $1286万
 $25,072/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
           <t>G | 513呎 (2房)
 $1267万
 $24,696/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -44189,7 +44189,7 @@
           <t>A | 819呎 (3房)
 $3054万
 $37,291/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -44213,7 +44213,7 @@
           <t>D | 432呎 (2房)
 $1193万
 $27,606/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -44268,7 +44268,7 @@
           <t>A | 819呎 (3房)
 $3024万
 $36,921/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -44276,7 +44276,7 @@
           <t>B | 818呎 (3房)
 $3730万
 $45,605/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
@@ -44284,7 +44284,7 @@
           <t>C | 319呎 (1房)
 $845万
 $26,495/呎
-(26年-06月)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -44363,7 +44363,7 @@
           <t>C | 320呎 (1房)
 $837万
 $26,150/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -44371,7 +44371,7 @@
           <t>D | 432呎 (2房)
 $1169万
 $27,062/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -44379,7 +44379,7 @@
           <t>E | 453呎 (2房)
 $1280万
 $28,267/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -44426,7 +44426,7 @@
           <t>A | 819呎 (3房)
 $4034万
 $49,252/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -44434,7 +44434,7 @@
           <t>B | 818呎 (3房)
 $3867万
 $47,278/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -44442,7 +44442,7 @@
           <t>C | 320呎 (1房)
 $828万
 $25,891/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -44450,7 +44450,7 @@
           <t>D | 432呎 (2房)
 $1158万
 $26,796/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -44505,7 +44505,7 @@
           <t>A | 819呎 (3房)
 $3287万
 $40,136/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44521,7 +44521,7 @@
           <t>C | 320呎 (1房)
 $797万
 $24,903/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -44529,7 +44529,7 @@
           <t>D | 432呎 (2房)
 $1124万
 $26,019/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -44584,7 +44584,7 @@
           <t>A | 819呎 (3房)
 $3066万
 $37,441/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -44592,7 +44592,7 @@
           <t>B | 818呎 (3房)
 $2950万
 $36,070/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
@@ -44600,7 +44600,7 @@
           <t>C | 320呎 (1房)
 $793万
 $24,778/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -44608,7 +44608,7 @@
           <t>D | 432呎 (2房)
 $1096万
 $25,382/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -44616,7 +44616,7 @@
           <t>E | 452呎 (2房)
 $1226万
 $27,122/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -44663,7 +44663,7 @@
           <t>A | 819呎 (3房)
 $2993万
 $36,545/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -44671,7 +44671,7 @@
           <t>B | 818呎 (3房)
 $2991万
 $36,566/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
@@ -44679,7 +44679,7 @@
           <t>C | 320呎 (1房)
 $789万
 $24,656/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -44687,7 +44687,7 @@
           <t>D | 432呎 (2房)
 $1091万
 $25,255/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="F14" s="24" t="inlineStr">
@@ -44695,7 +44695,7 @@
           <t>E | 452呎 (2房)
 $1248万
 $27,602/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -44742,7 +44742,7 @@
           <t>A | 819呎 (3房)
 $2949万
 $36,009/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -44758,7 +44758,7 @@
           <t>C | 320呎 (1房)
 $770万
 $24,050/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -44766,7 +44766,7 @@
           <t>D | 432呎 (2房)
 $1086万
 $25,130/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -44821,7 +44821,7 @@
           <t>A | 819呎 (3房)
 $2934万
 $35,829/呎
-(25年-10月)</t>
+(25年-10月-26日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -44829,7 +44829,7 @@
           <t>B | 818呎 (3房)
 $2907万
 $35,533/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
@@ -44837,7 +44837,7 @@
           <t>C | 320呎 (1房)
 $781万
 $24,412/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -44845,7 +44845,7 @@
           <t>D | 432呎 (2房)
 $1102万
 $25,507/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
@@ -44900,7 +44900,7 @@
           <t>A | 819呎 (3房)
 $2920万
 $35,653/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -44908,7 +44908,7 @@
           <t>B | 818呎 (3房)
 $2838万
 $34,689/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
@@ -44916,7 +44916,7 @@
           <t>C | 320呎 (1房)
 $777万
 $24,291/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -44924,7 +44924,7 @@
           <t>D | 432呎 (2房)
 $1096万
 $25,377/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -44979,7 +44979,7 @@
           <t>A | 819呎 (3房)
 $2906万
 $35,480/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -44987,7 +44987,7 @@
           <t>B | 818呎 (3房)
 $2796万
 $34,185/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
@@ -44995,7 +44995,7 @@
           <t>C | 320呎 (1房)
 $758万
 $23,694/呎
-(26年-03月)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -45003,7 +45003,7 @@
           <t>D | 432呎 (2房)
 $1069万
 $24,755/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -45058,7 +45058,7 @@
           <t>A | 819呎 (3房)
 $2835万
 $34,613/呎
-(25年-09月)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
@@ -45066,7 +45066,7 @@
           <t>B | 818呎 (3房)
 $2702万
 $33,029/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
@@ -45074,7 +45074,7 @@
           <t>C | 320呎 (1房)
 $770万
 $24,047/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -45082,7 +45082,7 @@
           <t>D | 432呎 (2房)
 $1064万
 $24,632/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -45090,7 +45090,7 @@
           <t>E | 452呎 (2房)
 $1167万
 $25,825/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -45137,7 +45137,7 @@
           <t>A | 819呎 (3房)
 $2823万
 $34,466/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -45145,7 +45145,7 @@
           <t>B | 818呎 (3房)
 $2822万
 $34,501/呎
-(26年-03月)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
@@ -45153,7 +45153,7 @@
           <t>C | 319呎 (1房)
 $768万
 $24,066/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -45161,7 +45161,7 @@
           <t>D | 432呎 (2房)
 $1080万
 $25,000/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -45169,7 +45169,7 @@
           <t>E | 452呎 (2房)
 $1162万
 $25,697/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -45295,7 +45295,7 @@
           <t>A | 819呎 (3房)
 $2834万
 $34,601/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -45303,7 +45303,7 @@
           <t>B | 818呎 (3房)
 $2701万
 $33,015/呎
-(26年-01月)</t>
+(26年-01月-01日)</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
@@ -45311,7 +45311,7 @@
           <t>C | 320呎 (1房)
 $754万
 $23,569/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -45319,7 +45319,7 @@
           <t>D | 432呎 (2房)
 $1064万
 $24,627/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -45327,7 +45327,7 @@
           <t>E | 452呎 (2房)
 $1122万
 $24,827/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -45374,7 +45374,7 @@
           <t>A | 819呎 (3房)
 $2792万
 $34,088/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -45382,7 +45382,7 @@
           <t>B | 818呎 (3房)
 $2713万
 $33,171/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
@@ -45390,7 +45390,7 @@
           <t>C | 320呎 (1房)
 $750万
 $23,453/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -45398,7 +45398,7 @@
           <t>D | 432呎 (2房)
 $1038万
 $24,021/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -45406,7 +45406,7 @@
           <t>E | 452呎 (2房)
 $1116万
 $24,701/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -45453,7 +45453,7 @@
           <t>A | 819呎 (3房)
 $2751万
 $33,587/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -45461,7 +45461,7 @@
           <t>B | 818呎 (3房)
 $2622万
 $32,051/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
@@ -45469,7 +45469,7 @@
           <t>C | 320呎 (1房)
 $732万
 $22,875/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -45477,7 +45477,7 @@
           <t>D | 432呎 (2房)
 $1032万
 $23,900/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -45485,7 +45485,7 @@
           <t>E | 452呎 (2房)
 $1111万
 $24,577/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -45532,7 +45532,7 @@
           <t>A | 819呎 (3房)
 $2736万
 $33,410/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -45540,7 +45540,7 @@
           <t>B | 818呎 (3房)
 $2608万
 $31,884/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
@@ -45548,7 +45548,7 @@
           <t>C | 320呎 (1房)
 $728万
 $22,762/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -45556,7 +45556,7 @@
           <t>D | 432呎 (2房)
 $1027万
 $23,782/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -45564,7 +45564,7 @@
           <t>E | 452呎 (2房)
 $1105万
 $24,456/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -45611,7 +45611,7 @@
           <t>A | 819呎 (3房)
 $2806万
 $34,261/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -45619,7 +45619,7 @@
           <t>B | 818呎 (3房)
 $2595万
 $31,724/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
@@ -45627,7 +45627,7 @@
           <t>C | 320呎 (1房)
 $725万
 $22,647/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -45635,7 +45635,7 @@
           <t>D | 432呎 (2房)
 $1022万
 $23,664/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -45643,7 +45643,7 @@
           <t>E | 452呎 (2房)
 $1100万
 $24,332/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -45690,7 +45690,7 @@
           <t>A | 819呎 (3房)
 $2792万
 $34,090/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -45698,7 +45698,7 @@
           <t>B | 818呎 (3房)
 $2582万
 $31,565/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
@@ -45706,7 +45706,7 @@
           <t>C | 320呎 (1房)
 $721万
 $22,534/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -45714,7 +45714,7 @@
           <t>D | 432呎 (2房)
 $1017万
 $23,544/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -45722,7 +45722,7 @@
           <t>E | 452呎 (2房)
 $1094万
 $24,210/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -45769,7 +45769,7 @@
           <t>A | 819呎 (3房)
 $2722万
 $33,242/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -45777,7 +45777,7 @@
           <t>B | 818呎 (3房)
 $2569万
 $31,407/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
@@ -45785,7 +45785,7 @@
           <t>C | 320呎 (1房)
 $718万
 $22,422/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -45793,7 +45793,7 @@
           <t>D | 432呎 (2房)
 $1022万
 $23,662/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
@@ -45801,7 +45801,7 @@
           <t>E | 452呎 (2房)
 $1089万
 $24,091/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -45848,7 +45848,7 @@
           <t>A | 819呎 (3房)
 $2682万
 $32,744/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -45856,7 +45856,7 @@
           <t>B | 818呎 (3房)
 $2531万
 $30,936/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
@@ -45864,7 +45864,7 @@
           <t>C | 320呎 (1房)
 $707万
 $22,084/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -45872,7 +45872,7 @@
           <t>D | 432呎 (2房)
 $1007万
 $23,308/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -45880,7 +45880,7 @@
           <t>E | 452呎 (2房)
 $1073万
 $23,730/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -45927,7 +45927,7 @@
           <t>A | 819呎 (3房)
 $2629万
 $32,098/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -45935,7 +45935,7 @@
           <t>B | 818呎 (3房)
 $2505万
 $30,627/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
@@ -45943,7 +45943,7 @@
           <t>C | 319呎 (1房)
 $716万
 $22,433/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -45951,7 +45951,7 @@
           <t>D | 432呎 (2房)
 $987万
 $22,845/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
@@ -45959,7 +45959,7 @@
           <t>E | 452呎 (2房)
 $1062万
 $23,493/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -46006,7 +46006,7 @@
           <t>A | 819呎 (3房)
 $2603万
 $31,780/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -46014,7 +46014,7 @@
           <t>B | 818呎 (3房)
 $2480万
 $30,320/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
@@ -46022,7 +46022,7 @@
           <t>C | 319呎 (1房)
 $708万
 $22,207/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -46030,7 +46030,7 @@
           <t>D | 431呎 (2房)
 $999万
 $23,183/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -46038,7 +46038,7 @@
           <t>E | 452呎 (2房)
 $1051万
 $23,257/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -46085,7 +46085,7 @@
           <t>A | 819呎 (3房)
 $2563万
 $31,297/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -46093,7 +46093,7 @@
           <t>B | 818呎 (3房)
 $2443万
 $29,866/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
@@ -46101,7 +46101,7 @@
           <t>C | 320呎 (1房)
 $682万
 $21,322/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -46109,7 +46109,7 @@
           <t>D | 432呎 (2房)
 $962万
 $22,278/呎
-(26年-01月)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="F32" s="24" t="inlineStr">
@@ -46117,7 +46117,7 @@
           <t>E | 452呎 (2房)
 $1036万
 $22,909/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -46164,7 +46164,7 @@
           <t>A | 819呎 (3房)
 $2525万
 $30,827/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -46172,7 +46172,7 @@
           <t>B | 818呎 (3房)
 $2406万
 $29,418/呎
-(25年-09月)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
@@ -46180,7 +46180,7 @@
           <t>C | 320呎 (1房)
 $672万
 $21,000/呎
-(26年-01月)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -46188,7 +46188,7 @@
           <t>D | 432呎 (2房)
 $948万
 $21,942/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -46196,7 +46196,7 @@
           <t>E | 452呎 (2房)
 $1020万
 $22,564/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -46881,7 +46881,7 @@
           <t>B | 449呎 (2房)
 $1251万
 $27,853/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -46936,7 +46936,7 @@
           <t>B | 449呎 (2房)
 $1198万
 $26,670/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -47038,7 +47038,7 @@
           <t>A | 548呎 (2房)
 $1565万
 $28,560/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -47101,7 +47101,7 @@
           <t>B | 449呎 (2房)
 $1180万
 $26,274/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -47156,7 +47156,7 @@
           <t>B | 449呎 (2房)
 $1151万
 $25,628/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -47211,7 +47211,7 @@
           <t>B | 449呎 (2房)
 $1145万
 $25,501/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -47313,7 +47313,7 @@
           <t>A | 548呎 (2房)
 $1519万
 $27,714/呎
-(26年-07月)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
@@ -47321,7 +47321,7 @@
           <t>B | 449呎 (2房)
 $1150万
 $25,624/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -47368,7 +47368,7 @@
           <t>A | 548呎 (2房)
 $1511万
 $27,577/呎
-(26年-06月)</t>
+(26年-06月-20日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -47376,7 +47376,7 @@
           <t>B | 449呎 (2房)
 $1145万
 $25,494/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -47431,7 +47431,7 @@
           <t>B | 449呎 (2房)
 $1139万
 $25,367/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -47486,7 +47486,7 @@
           <t>B | 449呎 (2房)
 $1111万
 $24,744/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -47541,7 +47541,7 @@
           <t>B | 449呎 (2房)
 $1106万
 $24,621/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -47596,7 +47596,7 @@
           <t>B | 449呎 (2房)
 $1100万
 $24,499/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -47643,7 +47643,7 @@
           <t>A | 548呎 (2房)
 $1474万
 $26,894/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -47651,7 +47651,7 @@
           <t>B | 449呎 (2房)
 $1116万
 $24,864/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -47698,7 +47698,7 @@
           <t>A | 548呎 (2房)
 $1452万
 $26,489/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -47706,7 +47706,7 @@
           <t>B | 449呎 (2房)
 $1078万
 $24,009/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -47761,7 +47761,7 @@
           <t>B | 449呎 (2房)
 $1089万
 $24,247/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -47816,7 +47816,7 @@
           <t>B | 449呎 (2房)
 $1057万
 $23,532/呎
-(25年-12月)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -47871,7 +47871,7 @@
           <t>B | 449呎 (2房)
 $1041万
 $23,178/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -47926,7 +47926,7 @@
           <t>B | 449呎 (2房)
 $1025万
 $22,831/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -48508,7 +48508,7 @@
           <t>C | 309呎 (1房)
 $828万
 $26,812/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -48603,7 +48603,7 @@
           <t>G | 513呎 (2房)
 $1591万
 $31,006/呎
-(26年-07月)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -48666,7 +48666,7 @@
           <t>G | 513呎 (2房)
 $1553万
 $30,281/呎
-(26年-06月)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
     </row>
@@ -48729,7 +48729,7 @@
           <t>G | 513呎 (2房)
 $1487万
 $28,992/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -48792,7 +48792,7 @@
           <t>G | 513呎 (2房)
 $1538万
 $29,979/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -48855,7 +48855,7 @@
           <t>G | 513呎 (2房)
 $1501万
 $29,267/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -48918,7 +48918,7 @@
           <t>G | 513呎 (2房)
 $1494万
 $29,121/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -48981,7 +48981,7 @@
           <t>G | 513呎 (2房)
 $1458万
 $28,419/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -49044,7 +49044,7 @@
           <t>G | 513呎 (2房)
 $1451万
 $28,279/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -49107,7 +49107,7 @@
           <t>G | 513呎 (2房)
 $1443万
 $28,135/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -49233,7 +49233,7 @@
           <t>G | 513呎 (2房)
 $1422万
 $27,715/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -49296,7 +49296,7 @@
           <t>G | 513呎 (2房)
 $1387万
 $27,035/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
     </row>
@@ -49359,7 +49359,7 @@
           <t>G | 513呎 (2房)
 $1380万
 $26,901/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -49422,7 +49422,7 @@
           <t>G | 513呎 (2房)
 $1373万
 $26,766/呎
-(26年-01月)</t>
+(26年-01月-19日)</t>
         </is>
       </c>
     </row>
@@ -49485,7 +49485,7 @@
           <t>G | 513呎 (2房)
 $1366万
 $26,632/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -49548,7 +49548,7 @@
           <t>G | 513呎 (2房)
 $1359万
 $26,499/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -49611,7 +49611,7 @@
           <t>G | 513呎 (2房)
 $1353万
 $26,366/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
     </row>
@@ -49674,7 +49674,7 @@
           <t>G | 513呎 (2房)
 $1347万
 $26,265/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -49737,7 +49737,7 @@
           <t>G | 513呎 (2房)
 $1334万
 $26,004/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -49800,7 +49800,7 @@
           <t>G | 513呎 (2房)
 $1306万
 $25,454/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -49863,7 +49863,7 @@
           <t>G | 513呎 (2房)
 $1286万
 $25,072/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
     </row>
@@ -49926,7 +49926,7 @@
           <t>G | 513呎 (2房)
 $1267万
 $24,696/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-维港．湾畔第1A期.xlsx
+++ b/files/九龙-启德-维港．湾畔第1A期.xlsx
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3898,14 +3898,14 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
         <v>12805000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>28267</v>
+        <v>28330</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>12805000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>28267</v>
+        <v>28330</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -21557,12 +21557,12 @@
       </c>
       <c r="H314" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I314" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J314" s="3" t="inlineStr">
@@ -21572,12 +21572,12 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M314" s="3" t="inlineStr">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -25680,14 +25680,14 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
-        <v>15112000</v>
+        <v>5130000</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>27577</v>
+        <v>9361</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
@@ -25695,10 +25695,10 @@
         </is>
       </c>
       <c r="K374" s="5" t="n">
-        <v>15112000</v>
+        <v>5130000</v>
       </c>
       <c r="L374" s="5" t="n">
-        <v>27577</v>
+        <v>9361</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
@@ -28947,7 +28947,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -28957,12 +28957,12 @@
       </c>
       <c r="H422" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I422" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J422" s="3" t="inlineStr">
@@ -28972,12 +28972,12 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M422" s="3" t="inlineStr">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="N422" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -44376,10 +44376,10 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>E | 453呎 (2房)
+          <t>E | 452呎 (2房)
 $1280万
-$28,267/呎
-(26年-06月-28日)</t>
+$28,330/呎
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -46311,7 +46311,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -46326,7 +46326,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>133</t>
         </is>
       </c>
     </row>
@@ -46813,12 +46813,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -47366,9 +47366,9 @@
       <c r="B23" s="24" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
-$1511万
-$27,577/呎
-(26年-06月-20日)</t>
+$513万
+$9,361/呎
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
@@ -47803,12 +47803,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 548呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
